--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>121159683</v>
       </c>
       <c r="B3" t="n">
-        <v>100355</v>
+        <v>100365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>121159676</v>
       </c>
       <c r="B4" t="n">
-        <v>103211</v>
+        <v>103221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>121159683</v>
       </c>
       <c r="B3" t="n">
-        <v>100365</v>
+        <v>100378</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>121159676</v>
       </c>
       <c r="B4" t="n">
-        <v>103221</v>
+        <v>103234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>121159683</v>
       </c>
       <c r="B3" t="n">
-        <v>100378</v>
+        <v>100379</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>121159676</v>
       </c>
       <c r="B4" t="n">
-        <v>103234</v>
+        <v>103235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>121159683</v>
       </c>
       <c r="B3" t="n">
-        <v>100379</v>
+        <v>100382</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>121159676</v>
       </c>
       <c r="B4" t="n">
-        <v>103235</v>
+        <v>103238</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121159683</v>
+        <v>121159676</v>
       </c>
       <c r="B3" t="n">
-        <v>100382</v>
+        <v>103238</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222886</v>
+        <v>222395</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -911,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121159676</v>
+        <v>121159683</v>
       </c>
       <c r="B4" t="n">
-        <v>103238</v>
+        <v>100382</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,25 +923,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222395</v>
+        <v>222886</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Backsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Pulsatilla vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>121159676</v>
       </c>
       <c r="B3" t="n">
-        <v>103238</v>
+        <v>103244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>121159683</v>
       </c>
       <c r="B4" t="n">
-        <v>100382</v>
+        <v>100388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>69119112</v>
       </c>
       <c r="B2" t="n">
-        <v>88994</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405840.0540027868</v>
+        <v>405840</v>
       </c>
       <c r="R2" t="n">
-        <v>6198346.331528366</v>
+        <v>6198346</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2017-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121159676</v>
+        <v>113670982</v>
       </c>
       <c r="B3" t="n">
-        <v>103244</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,37 +791,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222395</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Snapphanabacken, björkhage 100 m söder, Sk</t>
+          <t>700 m SO Snapphanabacken, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405749</v>
+        <v>406043</v>
       </c>
       <c r="R3" t="n">
-        <v>6198594</v>
+        <v>6198233</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,17 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1946-05-26</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1946-05-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inventerad av Gunnar Olsson</t>
+          <t>2023-07-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,59 +864,50 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Björkhage</t>
+          <t>källdrag i hagmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skånes Flora, Höör socken, 1946-1947</t>
-        </is>
-      </c>
+          <t>Torbjörn Tyler, Linda Birkedal</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121159683</v>
+        <v>121159672</v>
       </c>
       <c r="B4" t="n">
-        <v>100388</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222886</v>
+        <v>220075</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Backsippa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1020,6 +986,330 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skånes Flora, Höör socken, 1946-1947</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113670980</v>
+      </c>
+      <c r="B5" t="n">
+        <v>111129</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>700 m SO Snapphanabacken, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>406043</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6198233</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>källdrag i hagmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler, Linda Birkedal</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121159676</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104253</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Snapphanabacken, björkhage 100 m söder, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>405749</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6198594</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1946-05-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1946-05-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Inventerad av Gunnar Olsson</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Björkhage</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skånes Flora, Höör socken, 1946-1947</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121159683</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101346</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222886</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Backsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Snapphanabacken, björkhage 100 m söder, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>405749</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6198594</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1946-05-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1946-05-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Inventerad av Gunnar Olsson</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Björkhage</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>

--- a/artfynd/A 19517-2023 artfynd.xlsx
+++ b/artfynd/A 19517-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69119112</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113670982</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121159672</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113670980</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1203,6 +1228,11 @@
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121159676</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,8 +1344,21 @@
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121159683</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>